--- a/szablon.xlsx
+++ b/szablon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\konwe\TR_PBC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABBB106-720D-4F7B-BA0D-FF701458A190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F128055-B68E-417C-91D1-E6A93DE61572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
     <t>Statystyki: Zasięg CCS i Estymacja na populację, Populacja w wybranej grupie celowej = 29400927</t>
   </si>
   <si>
-    <t>Fale: 1/2025-12/2025</t>
+    <t>Fale: 4/2025-3/2026</t>
   </si>
 </sst>
 </file>

--- a/szablon.xlsx
+++ b/szablon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\konwe\TR_PBC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F128055-B68E-417C-91D1-E6A93DE61572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEC9307-F5DF-4008-905C-EFABC458AE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
     <t>Statystyki: Zasięg CCS i Estymacja na populację, Populacja w wybranej grupie celowej = 29400927</t>
   </si>
   <si>
-    <t>Fale: 4/2025-3/2026</t>
+    <t>Fale: 7/2025-6/2026</t>
   </si>
 </sst>
 </file>
